--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8319,0.0118,0.0669,0.0457</t>
-  </si>
-  <si>
-    <t>0.0007,0.0019,0.0006,0.9991</t>
-  </si>
-  <si>
-    <t>0.7134,0.0251,0.0234,0.2261</t>
-  </si>
-  <si>
-    <t>0.0170,0.0145,0.0030,0.9870</t>
-  </si>
-  <si>
-    <t>0.9944,0.0031,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9924,0.0079,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9863,0.0036,0.0012,0.0046</t>
-  </si>
-  <si>
-    <t>0.9921,0.0027,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9901,0.0058,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9900,0.0063,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9931,0.0033,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9886,0.0016,0.0002,0.0050</t>
-  </si>
-  <si>
-    <t>0.7813,0.0941,0.1160,0.0192</t>
-  </si>
-  <si>
-    <t>0.1606,0.0247,0.8741,0.0030</t>
-  </si>
-  <si>
-    <t>0.3246,0.0413,0.7203,0.0038</t>
-  </si>
-  <si>
-    <t>0.1703,0.0065,0.8933,0.0027</t>
-  </si>
-  <si>
-    <t>0.4301,0.0174,0.6901,0.0031</t>
-  </si>
-  <si>
-    <t>0.0046,0.9878,0.0280,0.0004</t>
-  </si>
-  <si>
-    <t>0.0187,0.9755,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.4948,0.4824,0.1060,0.0050</t>
-  </si>
-  <si>
-    <t>0.0122,0.9792,0.0113,0.0011</t>
-  </si>
-  <si>
-    <t>0.0120,0.9803,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.4617,0.0242,0.6026,0.0133</t>
-  </si>
-  <si>
-    <t>0.3119,0.0475,0.6775,0.0278</t>
-  </si>
-  <si>
-    <t>0.0097,0.0011,0.9900,0.0016</t>
-  </si>
-  <si>
-    <t>0.1386,0.0100,0.8826,0.0138</t>
-  </si>
-  <si>
-    <t>0.0406,0.0148,0.9487,0.0099</t>
-  </si>
-  <si>
-    <t>0.0082,0.0024,0.9910,0.0011</t>
-  </si>
-  <si>
-    <t>0.0015,0.0022,0.9968,0.0007</t>
-  </si>
-  <si>
-    <t>0.8676,0.0988,0.0436,0.0045</t>
-  </si>
-  <si>
-    <t>0.5392,0.1031,0.4576,0.0113</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9971,0.0041</t>
-  </si>
-  <si>
-    <t>0.0070,0.8163,0.6890,0.0016</t>
-  </si>
-  <si>
-    <t>0.8729,0.0593,0.0274,0.0200</t>
-  </si>
-  <si>
-    <t>0.1148,0.0210,0.9186,0.0064</t>
-  </si>
-  <si>
-    <t>0.8238,0.2116,0.0157,0.0026</t>
-  </si>
-  <si>
-    <t>0.1005,0.8255,0.2122,0.0102</t>
-  </si>
-  <si>
-    <t>0.0017,0.9254,0.5566,0.0080</t>
-  </si>
-  <si>
-    <t>0.0130,0.2771,0.9440,0.0020</t>
-  </si>
-  <si>
-    <t>0.0049,0.4841,0.9519,0.0007</t>
-  </si>
-  <si>
-    <t>0.0292,0.0171,0.9319,0.0494</t>
-  </si>
-  <si>
-    <t>0.0041,0.1433,0.9732,0.0004</t>
-  </si>
-  <si>
-    <t>0.0045,0.9658,0.1618,0.0012</t>
-  </si>
-  <si>
-    <t>0.0151,0.1913,0.9376,0.0060</t>
-  </si>
-  <si>
-    <t>0.4003,0.3748,0.1182,0.3665</t>
-  </si>
-  <si>
-    <t>0.0099,0.9307,0.0322,0.0693</t>
-  </si>
-  <si>
-    <t>0.0124,0.9606,0.0904,0.0009</t>
-  </si>
-  <si>
-    <t>0.0038,0.9833,0.0343,0.0025</t>
-  </si>
-  <si>
-    <t>0.0008,0.4398,0.9841,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.4459,0.9892,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.0036,0.9813,0.0109</t>
-  </si>
-  <si>
-    <t>0.0484,0.0017,0.9707,0.0018</t>
-  </si>
-  <si>
-    <t>0.0014,0.0202,0.9896,0.0041</t>
-  </si>
-  <si>
-    <t>0.0042,0.0120,0.9920,0.0005</t>
-  </si>
-  <si>
-    <t>0.9735,0.0235,0.0033,0.0018</t>
-  </si>
-  <si>
-    <t>0.9841,0.0040,0.0016,0.0038</t>
-  </si>
-  <si>
-    <t>0.9838,0.0085,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.0037,0.0415,0.9890,0.0014</t>
-  </si>
-  <si>
-    <t>0.9871,0.0037,0.0006,0.0031</t>
-  </si>
-  <si>
-    <t>0.9888,0.0083,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9784,0.0148,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.0003,0.7325,0.9805,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0153,0.9912,0.0041</t>
-  </si>
-  <si>
-    <t>0.0040,0.3054,0.9466,0.0054</t>
-  </si>
-  <si>
-    <t>0.0002,0.9430,0.9649,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0438,0.9944,0.0005</t>
-  </si>
-  <si>
-    <t>0.0128,0.9422,0.2068,0.0044</t>
-  </si>
-  <si>
-    <t>0.0149,0.9640,0.0771,0.0011</t>
-  </si>
-  <si>
-    <t>0.8876,0.0458,0.0602,0.0119</t>
-  </si>
-  <si>
-    <t>0.2349,0.0871,0.7894,0.0055</t>
-  </si>
-  <si>
-    <t>0.0008,0.0126,0.9969,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.8822,0.8623,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.8919,0.8877,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9847,0.6298,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9231,0.9501,0.0000</t>
-  </si>
-  <si>
-    <t>0.1242,0.0090,0.1146,0.7674</t>
-  </si>
-  <si>
-    <t>0.0004,0.0029,0.0018,0.9989</t>
-  </si>
-  <si>
-    <t>0.0026,0.0106,0.0007,0.9971</t>
-  </si>
-  <si>
-    <t>0.0129,0.0212,0.0052,0.9854</t>
-  </si>
-  <si>
-    <t>0.0009,0.0076,0.0006,0.9985</t>
-  </si>
-  <si>
-    <t>0.0014,0.0024,0.0032,0.9973</t>
-  </si>
-  <si>
-    <t>0.0062,0.8373,0.7982,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.7849,0.9614,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.8039,0.7680,0.0011</t>
-  </si>
-  <si>
-    <t>0.0084,0.5151,0.9095,0.0036</t>
-  </si>
-  <si>
-    <t>0.0002,0.9796,0.8769,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.8042,0.9437,0.0001</t>
-  </si>
-  <si>
-    <t>0.9929,0.0033,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9882,0.0062,0.0010,0.0014</t>
-  </si>
-  <si>
-    <t>0.9823,0.0122,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.9918,0.0034,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9828,0.0165,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9908,0.0061,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9861,0.0049,0.0008,0.0029</t>
-  </si>
-  <si>
-    <t>0.9886,0.0060,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.9944,0.0011,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9887,0.0066,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.9915,0.0027,0.0003,0.0023</t>
-  </si>
-  <si>
-    <t>0.9929,0.0038,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9913,0.0032,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9955,0.0022,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9915,0.0022,0.0004,0.0022</t>
-  </si>
-  <si>
-    <t>0.9888,0.0050,0.0008,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.0014,0.9956,0.0043</t>
-  </si>
-  <si>
-    <t>0.0444,0.0244,0.9535,0.0012</t>
-  </si>
-  <si>
-    <t>0.5695,0.0489,0.4227,0.0402</t>
-  </si>
-  <si>
-    <t>0.0515,0.0092,0.9447,0.0117</t>
-  </si>
-  <si>
-    <t>0.0285,0.9620,0.0071,0.0018</t>
-  </si>
-  <si>
-    <t>0.2055,0.8213,0.0126,0.0019</t>
-  </si>
-  <si>
-    <t>0.5670,0.5725,0.0057,0.0024</t>
-  </si>
-  <si>
-    <t>0.6837,0.4386,0.0070,0.0016</t>
-  </si>
-  <si>
-    <t>0.1583,0.8551,0.0293,0.0018</t>
-  </si>
-  <si>
-    <t>0.0128,0.9810,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9297,0.0970,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.6036,0.2072,0.2685,0.0344</t>
-  </si>
-  <si>
-    <t>0.0284,0.0109,0.9398,0.0423</t>
-  </si>
-  <si>
-    <t>0.4677,0.1331,0.4514,0.0172</t>
-  </si>
-  <si>
-    <t>0.5242,0.0432,0.4829,0.0215</t>
-  </si>
-  <si>
-    <t>0.1093,0.0305,0.0439,0.8884</t>
-  </si>
-  <si>
-    <t>0.0011,0.9864,0.0146,0.0174</t>
-  </si>
-  <si>
-    <t>0.0006,0.9909,0.0076,0.0149</t>
-  </si>
-  <si>
-    <t>0.0408,0.8614,0.0484,0.2125</t>
-  </si>
-  <si>
-    <t>0.0010,0.9565,0.7502,0.0004</t>
-  </si>
-  <si>
-    <t>0.0250,0.9500,0.1082,0.0012</t>
-  </si>
-  <si>
-    <t>0.7371,0.3253,0.0171,0.0010</t>
-  </si>
-  <si>
-    <t>0.8530,0.1947,0.0161,0.0032</t>
-  </si>
-  <si>
-    <t>0.9737,0.0146,0.0050,0.0037</t>
-  </si>
-  <si>
-    <t>0.9795,0.0039,0.0009,0.0070</t>
-  </si>
-  <si>
-    <t>0.9882,0.0019,0.0004,0.0037</t>
-  </si>
-  <si>
-    <t>0.9821,0.0047,0.0027,0.0034</t>
-  </si>
-  <si>
-    <t>0.9902,0.0027,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.9652,0.0248,0.0121,0.0022</t>
-  </si>
-  <si>
-    <t>0.9839,0.0017,0.0009,0.0061</t>
-  </si>
-  <si>
-    <t>0.9757,0.0063,0.0017,0.0058</t>
-  </si>
-  <si>
-    <t>0.0005,0.7241,0.9606,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.8649,0.8787,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.1503,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.0240,0.0881,0.9423,0.0012</t>
-  </si>
-  <si>
-    <t>0.5743,0.1133,0.3113,0.0915</t>
-  </si>
-  <si>
-    <t>0.5927,0.2727,0.1681,0.0227</t>
-  </si>
-  <si>
-    <t>0.2204,0.0029,0.7546,0.0304</t>
-  </si>
-  <si>
-    <t>0.6668,0.0302,0.2900,0.0350</t>
-  </si>
-  <si>
-    <t>0.2378,0.0193,0.0312,0.8057</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.0015,0.9997</t>
-  </si>
-  <si>
-    <t>0.0008,0.0495,0.0051,0.9950</t>
-  </si>
-  <si>
-    <t>0.0172,0.0063,0.0078,0.9841</t>
-  </si>
-  <si>
-    <t>0.0001,0.6526,0.9774,0.0002</t>
-  </si>
-  <si>
-    <t>0.9644,0.0202,0.0061,0.0045</t>
-  </si>
-  <si>
-    <t>0.7586,0.2982,0.0072,0.0038</t>
-  </si>
-  <si>
-    <t>0.9500,0.0388,0.0049,0.0057</t>
-  </si>
-  <si>
-    <t>0.8990,0.1302,0.0103,0.0020</t>
-  </si>
-  <si>
-    <t>0.9805,0.0033,0.0011,0.0066</t>
-  </si>
-  <si>
-    <t>0.1671,0.0042,0.0038,0.9053</t>
-  </si>
-  <si>
-    <t>0.9704,0.0015,0.0009,0.0180</t>
-  </si>
-  <si>
-    <t>0.0023,0.0348,0.9783,0.0095</t>
-  </si>
-  <si>
-    <t>0.0507,0.0008,0.0071,0.9637</t>
-  </si>
-  <si>
-    <t>0.7640,0.0028,0.0116,0.2015</t>
-  </si>
-  <si>
-    <t>0.7833,0.1891,0.0504,0.0126</t>
-  </si>
-  <si>
-    <t>0.8824,0.0452,0.0262,0.0238</t>
-  </si>
-  <si>
-    <t>0.8012,0.0626,0.1390,0.0070</t>
-  </si>
-  <si>
-    <t>0.4369,0.1996,0.4336,0.0307</t>
-  </si>
-  <si>
-    <t>0.5161,0.0827,0.4416,0.0039</t>
-  </si>
-  <si>
-    <t>0.7745,0.0950,0.1415,0.0162</t>
-  </si>
-  <si>
-    <t>0.9889,0.0018,0.0005,0.0040</t>
-  </si>
-  <si>
-    <t>0.9873,0.0047,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9893,0.0023,0.0005,0.0029</t>
-  </si>
-  <si>
-    <t>0.9836,0.0012,0.0007,0.0086</t>
-  </si>
-  <si>
-    <t>0.9877,0.0017,0.0002,0.0043</t>
-  </si>
-  <si>
-    <t>0.9849,0.0084,0.0032,0.0013</t>
-  </si>
-  <si>
-    <t>0.9868,0.0022,0.0005,0.0051</t>
-  </si>
-  <si>
-    <t>0.9753,0.0016,0.0006,0.0135</t>
-  </si>
-  <si>
-    <t>0.6749,0.3796,0.0293,0.0059</t>
-  </si>
-  <si>
-    <t>0.9529,0.0379,0.0117,0.0018</t>
-  </si>
-  <si>
-    <t>0.5021,0.5760,0.0137,0.0033</t>
-  </si>
-  <si>
-    <t>0.3562,0.5335,0.2347,0.0151</t>
-  </si>
-  <si>
-    <t>0.9026,0.1510,0.0057,0.0021</t>
-  </si>
-  <si>
-    <t>0.9727,0.0153,0.0034,0.0037</t>
-  </si>
-  <si>
-    <t>0.9636,0.0420,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.4679,0.6288,0.0090,0.0052</t>
-  </si>
-  <si>
-    <t>0.0003,0.0028,0.9984,0.0010</t>
-  </si>
-  <si>
-    <t>0.9253,0.0654,0.0153,0.0047</t>
-  </si>
-  <si>
-    <t>0.0011,0.0060,0.9972,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0195,0.9807,0.0041</t>
-  </si>
-  <si>
-    <t>0.1427,0.0047,0.9193,0.0022</t>
-  </si>
-  <si>
-    <t>0.0044,0.0762,0.9813,0.0012</t>
-  </si>
-  <si>
-    <t>0.0131,0.0084,0.9863,0.0006</t>
-  </si>
-  <si>
-    <t>0.0075,0.0036,0.9931,0.0002</t>
-  </si>
-  <si>
-    <t>0.0126,0.0023,0.9816,0.0043</t>
-  </si>
-  <si>
-    <t>0.5039,0.0686,0.4900,0.0219</t>
-  </si>
-  <si>
-    <t>0.2896,0.0115,0.8050,0.0052</t>
-  </si>
-  <si>
-    <t>0.3268,0.1280,0.5721,0.0085</t>
-  </si>
-  <si>
-    <t>0.2182,0.2277,0.5696,0.0136</t>
-  </si>
-  <si>
-    <t>0.0829,0.0981,0.8751,0.0091</t>
-  </si>
-  <si>
-    <t>0.4008,0.2946,0.2571,0.0055</t>
-  </si>
-  <si>
-    <t>0.6782,0.0340,0.3071,0.0132</t>
-  </si>
-  <si>
-    <t>0.7472,0.0643,0.1796,0.0116</t>
-  </si>
-  <si>
-    <t>0.3651,0.6960,0.0217,0.0029</t>
-  </si>
-  <si>
-    <t>0.8419,0.2980,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.7773,0.2906,0.0138,0.0034</t>
-  </si>
-  <si>
-    <t>0.9777,0.0304,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9248,0.0950,0.0096,0.0024</t>
-  </si>
-  <si>
-    <t>0.4587,0.1064,0.5032,0.0286</t>
-  </si>
-  <si>
-    <t>0.5624,0.0066,0.5110,0.0088</t>
-  </si>
-  <si>
-    <t>0.7311,0.0160,0.1180,0.0616</t>
-  </si>
-  <si>
-    <t>0.7285,0.0188,0.1982,0.0325</t>
-  </si>
-  <si>
-    <t>0.4141,0.0264,0.5077,0.1053</t>
-  </si>
-  <si>
-    <t>0.0028,0.0159,0.9450,0.1162</t>
-  </si>
-  <si>
-    <t>0.0294,0.1406,0.9090,0.0199</t>
-  </si>
-  <si>
-    <t>0.0035,0.1038,0.9855,0.0006</t>
-  </si>
-  <si>
-    <t>0.0043,0.0224,0.9867,0.0010</t>
-  </si>
-  <si>
-    <t>0.0021,0.2226,0.9593,0.0014</t>
-  </si>
-  <si>
-    <t>0.9931,0.0028,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9862,0.0084,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9884,0.0061,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9913,0.0061,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9811,0.0131,0.0023,0.0014</t>
-  </si>
-  <si>
-    <t>0.9908,0.0024,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.9908,0.0022,0.0004,0.0031</t>
-  </si>
-  <si>
-    <t>0.9740,0.0144,0.0027,0.0041</t>
-  </si>
-  <si>
-    <t>0.0606,0.0101,0.9273,0.0232</t>
-  </si>
-  <si>
-    <t>0.4182,0.1999,0.4931,0.0137</t>
-  </si>
-  <si>
-    <t>0.9346,0.0119,0.0062,0.0287</t>
-  </si>
-  <si>
-    <t>0.0013,0.0236,0.9939,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0626,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0240,0.1589,0.9020,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0046,0.9983,0.0007</t>
-  </si>
-  <si>
-    <t>0.0796,0.0862,0.8660,0.0109</t>
-  </si>
-  <si>
-    <t>0.0007,0.0245,0.9959,0.0008</t>
-  </si>
-  <si>
-    <t>0.0052,0.0094,0.9875,0.0016</t>
-  </si>
-  <si>
-    <t>0.4073,0.0930,0.5602,0.0176</t>
-  </si>
-  <si>
-    <t>0.3370,0.0025,0.7415,0.0069</t>
-  </si>
-  <si>
-    <t>0.7936,0.0085,0.1705,0.0172</t>
-  </si>
-  <si>
-    <t>0.7686,0.0427,0.1564,0.0208</t>
-  </si>
-  <si>
-    <t>0.9892,0.0055,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9683,0.0323,0.0043,0.0024</t>
-  </si>
-  <si>
-    <t>0.9890,0.0076,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9737,0.0164,0.0034,0.0028</t>
-  </si>
-  <si>
-    <t>0.9919,0.0021,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9868,0.0070,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.9930,0.0023,0.0004,0.0014</t>
-  </si>
-  <si>
-    <t>0.9903,0.0068,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.0187,0.6137,0.7710,0.0030</t>
-  </si>
-  <si>
-    <t>0.0004,0.0256,0.9959,0.0004</t>
-  </si>
-  <si>
-    <t>0.0074,0.2323,0.9588,0.0033</t>
-  </si>
-  <si>
-    <t>0.3035,0.0655,0.6795,0.0249</t>
-  </si>
-  <si>
-    <t>0.0003,0.0012,0.9957,0.0101</t>
-  </si>
-  <si>
-    <t>0.2938,0.0161,0.5012,0.1990</t>
-  </si>
-  <si>
-    <t>0.1275,0.0058,0.9035,0.0093</t>
-  </si>
-  <si>
-    <t>0.0066,0.1283,0.9765,0.0012</t>
-  </si>
-  <si>
-    <t>0.4100,0.0013,0.0047,0.7326</t>
-  </si>
-  <si>
-    <t>0.0097,0.0205,0.0155,0.9846</t>
-  </si>
-  <si>
-    <t>0.0088,0.0342,0.0103,0.9870</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.0005,0.9980</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.0012,0.9989</t>
-  </si>
-  <si>
-    <t>0.7982,0.0189,0.0449,0.1028</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7951,0.0085,0.0118,0.1431</t>
+  </si>
+  <si>
+    <t>0.0028,0.0064,0.0012,0.9971</t>
+  </si>
+  <si>
+    <t>0.1803,0.0038,0.0042,0.9045</t>
+  </si>
+  <si>
+    <t>0.0451,0.0087,0.0110,0.9679</t>
+  </si>
+  <si>
+    <t>0.9944,0.0019,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9939,0.0018,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9791,0.0127,0.0017,0.0029</t>
+  </si>
+  <si>
+    <t>0.9907,0.0027,0.0005,0.0028</t>
+  </si>
+  <si>
+    <t>0.9893,0.0027,0.0002,0.0026</t>
+  </si>
+  <si>
+    <t>0.9853,0.0100,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9937,0.0010,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9946,0.0015,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.5892,0.0465,0.4321,0.0161</t>
+  </si>
+  <si>
+    <t>0.3542,0.0194,0.7546,0.0020</t>
+  </si>
+  <si>
+    <t>0.2121,0.0140,0.8677,0.0023</t>
+  </si>
+  <si>
+    <t>0.0088,0.0040,0.9890,0.0005</t>
+  </si>
+  <si>
+    <t>0.5717,0.0160,0.4512,0.0239</t>
+  </si>
+  <si>
+    <t>0.0028,0.9940,0.0039,0.0003</t>
+  </si>
+  <si>
+    <t>0.0019,0.9950,0.0034,0.0004</t>
+  </si>
+  <si>
+    <t>0.4228,0.6408,0.0244,0.0032</t>
+  </si>
+  <si>
+    <t>0.0087,0.9861,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.0158,0.9778,0.0074,0.0012</t>
+  </si>
+  <si>
+    <t>0.5413,0.0981,0.4071,0.0662</t>
+  </si>
+  <si>
+    <t>0.3288,0.0272,0.6933,0.0355</t>
+  </si>
+  <si>
+    <t>0.0066,0.0019,0.9909,0.0013</t>
+  </si>
+  <si>
+    <t>0.2278,0.0139,0.8138,0.0070</t>
+  </si>
+  <si>
+    <t>0.0179,0.0029,0.9778,0.0036</t>
+  </si>
+  <si>
+    <t>0.0123,0.0032,0.9788,0.0089</t>
+  </si>
+  <si>
+    <t>0.0042,0.0049,0.9918,0.0019</t>
+  </si>
+  <si>
+    <t>0.7717,0.2423,0.0292,0.0051</t>
+  </si>
+  <si>
+    <t>0.7028,0.0775,0.2654,0.0190</t>
+  </si>
+  <si>
+    <t>0.0028,0.0073,0.9922,0.0031</t>
+  </si>
+  <si>
+    <t>0.0094,0.8853,0.4183,0.0007</t>
+  </si>
+  <si>
+    <t>0.8047,0.1174,0.0707,0.0287</t>
+  </si>
+  <si>
+    <t>0.1865,0.0393,0.8550,0.0087</t>
+  </si>
+  <si>
+    <t>0.9281,0.0814,0.0063,0.0023</t>
+  </si>
+  <si>
+    <t>0.0490,0.8800,0.1526,0.0237</t>
+  </si>
+  <si>
+    <t>0.0076,0.7667,0.8127,0.0044</t>
+  </si>
+  <si>
+    <t>0.0101,0.4467,0.9321,0.0017</t>
+  </si>
+  <si>
+    <t>0.0029,0.0566,0.9828,0.0039</t>
+  </si>
+  <si>
+    <t>0.0317,0.0098,0.9466,0.0244</t>
+  </si>
+  <si>
+    <t>0.0296,0.2663,0.9075,0.0068</t>
+  </si>
+  <si>
+    <t>0.0013,0.9673,0.3649,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.1462,0.9751,0.0021</t>
+  </si>
+  <si>
+    <t>0.1445,0.3535,0.0110,0.8130</t>
+  </si>
+  <si>
+    <t>0.0072,0.9626,0.0076,0.0249</t>
+  </si>
+  <si>
+    <t>0.0104,0.9569,0.0878,0.0020</t>
+  </si>
+  <si>
+    <t>0.0032,0.9820,0.0747,0.0018</t>
+  </si>
+  <si>
+    <t>0.0003,0.3830,0.9906,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0504,0.9943,0.0005</t>
+  </si>
+  <si>
+    <t>0.1027,0.0279,0.9049,0.0067</t>
+  </si>
+  <si>
+    <t>0.0279,0.0029,0.9766,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.0472,0.9753,0.0085</t>
+  </si>
+  <si>
+    <t>0.0010,0.0020,0.9968,0.0014</t>
+  </si>
+  <si>
+    <t>0.9359,0.1081,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.9839,0.0044,0.0015,0.0043</t>
+  </si>
+  <si>
+    <t>0.9732,0.0148,0.0023,0.0046</t>
+  </si>
+  <si>
+    <t>0.0004,0.0109,0.9962,0.0019</t>
+  </si>
+  <si>
+    <t>0.9817,0.0091,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.9873,0.0087,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9502,0.0387,0.0087,0.0045</t>
+  </si>
+  <si>
+    <t>0.0003,0.6433,0.9859,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0323,0.9952,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.0407,0.9952,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.8178,0.9876,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0482,0.8531,0.2698,0.0066</t>
+  </si>
+  <si>
+    <t>0.0007,0.9957,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.6398,0.0568,0.3367,0.0323</t>
+  </si>
+  <si>
+    <t>0.7222,0.2236,0.1065,0.0108</t>
+  </si>
+  <si>
+    <t>0.0050,0.1427,0.9771,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.9753,0.7260,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9279,0.8828,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9596,0.8533,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.8619,0.9422,0.0002</t>
+  </si>
+  <si>
+    <t>0.0193,0.0019,0.1453,0.8971</t>
+  </si>
+  <si>
+    <t>0.0003,0.0060,0.0005,0.9993</t>
+  </si>
+  <si>
+    <t>0.0045,0.0567,0.0060,0.9903</t>
+  </si>
+  <si>
+    <t>0.0033,0.0047,0.0044,0.9957</t>
+  </si>
+  <si>
+    <t>0.0140,0.0096,0.0145,0.9827</t>
+  </si>
+  <si>
+    <t>0.0017,0.0034,0.0009,0.9980</t>
+  </si>
+  <si>
+    <t>0.0002,0.9459,0.9509,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.4625,0.9883,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.7786,0.9012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.3826,0.9688,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9887,0.7555,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.6076,0.9610,0.0001</t>
+  </si>
+  <si>
+    <t>0.9753,0.0208,0.0045,0.0021</t>
+  </si>
+  <si>
+    <t>0.9836,0.0104,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9835,0.0100,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9887,0.0070,0.0009,0.0016</t>
+  </si>
+  <si>
+    <t>0.9880,0.0093,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9893,0.0064,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9893,0.0025,0.0004,0.0025</t>
+  </si>
+  <si>
+    <t>0.9778,0.0231,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.9932,0.0011,0.0001,0.0022</t>
+  </si>
+  <si>
+    <t>0.9936,0.0034,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9930,0.0037,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9953,0.0027,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0038,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9900,0.0051,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9897,0.0024,0.0007,0.0027</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.9964,0.0022</t>
+  </si>
+  <si>
+    <t>0.0293,0.2147,0.8963,0.0072</t>
+  </si>
+  <si>
+    <t>0.4968,0.0238,0.5563,0.0201</t>
+  </si>
+  <si>
+    <t>0.0182,0.0013,0.9863,0.0009</t>
+  </si>
+  <si>
+    <t>0.0482,0.9419,0.0150,0.0014</t>
+  </si>
+  <si>
+    <t>0.1535,0.8717,0.0101,0.0034</t>
+  </si>
+  <si>
+    <t>0.1688,0.8648,0.0070,0.0022</t>
+  </si>
+  <si>
+    <t>0.3817,0.6976,0.0123,0.0034</t>
+  </si>
+  <si>
+    <t>0.0591,0.9465,0.0049,0.0013</t>
+  </si>
+  <si>
+    <t>0.0147,0.9783,0.0024,0.0017</t>
+  </si>
+  <si>
+    <t>0.8748,0.1349,0.0239,0.0032</t>
+  </si>
+  <si>
+    <t>0.3552,0.3782,0.0393,0.2738</t>
+  </si>
+  <si>
+    <t>0.1044,0.0116,0.9294,0.0021</t>
+  </si>
+  <si>
+    <t>0.5681,0.1455,0.3368,0.0436</t>
+  </si>
+  <si>
+    <t>0.3376,0.0358,0.6627,0.0479</t>
+  </si>
+  <si>
+    <t>0.4232,0.1104,0.3024,0.3575</t>
+  </si>
+  <si>
+    <t>0.0018,0.9859,0.0177,0.0067</t>
+  </si>
+  <si>
+    <t>0.0023,0.9754,0.0085,0.0503</t>
+  </si>
+  <si>
+    <t>0.0486,0.9121,0.0488,0.0236</t>
+  </si>
+  <si>
+    <t>0.0009,0.9599,0.7917,0.0006</t>
+  </si>
+  <si>
+    <t>0.0151,0.9192,0.4073,0.0015</t>
+  </si>
+  <si>
+    <t>0.9354,0.0580,0.0152,0.0041</t>
+  </si>
+  <si>
+    <t>0.7601,0.3224,0.0121,0.0011</t>
+  </si>
+  <si>
+    <t>0.9795,0.0110,0.0039,0.0029</t>
+  </si>
+  <si>
+    <t>0.9697,0.0021,0.0007,0.0200</t>
+  </si>
+  <si>
+    <t>0.9906,0.0007,0.0002,0.0048</t>
+  </si>
+  <si>
+    <t>0.9788,0.0039,0.0010,0.0066</t>
+  </si>
+  <si>
+    <t>0.9903,0.0021,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9729,0.0168,0.0058,0.0025</t>
+  </si>
+  <si>
+    <t>0.9891,0.0018,0.0007,0.0029</t>
+  </si>
+  <si>
+    <t>0.9909,0.0019,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.0006,0.8289,0.9370,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.5935,0.9184,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.7585,0.9094,0.0003</t>
+  </si>
+  <si>
+    <t>0.0103,0.1342,0.9557,0.0006</t>
+  </si>
+  <si>
+    <t>0.3585,0.2188,0.0548,0.5128</t>
+  </si>
+  <si>
+    <t>0.7007,0.0312,0.2319,0.0281</t>
+  </si>
+  <si>
+    <t>0.4622,0.0063,0.6699,0.0036</t>
+  </si>
+  <si>
+    <t>0.5956,0.2078,0.2644,0.0557</t>
+  </si>
+  <si>
+    <t>0.0267,0.0043,0.0037,0.9835</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.0008,0.9997</t>
+  </si>
+  <si>
+    <t>0.0021,0.0714,0.0015,0.9947</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.0010,0.9983</t>
+  </si>
+  <si>
+    <t>0.0003,0.9044,0.9329,0.0001</t>
+  </si>
+  <si>
+    <t>0.9741,0.0142,0.0048,0.0030</t>
+  </si>
+  <si>
+    <t>0.2875,0.7574,0.0065,0.0046</t>
+  </si>
+  <si>
+    <t>0.9712,0.0025,0.0009,0.0170</t>
+  </si>
+  <si>
+    <t>0.9435,0.0463,0.0021,0.0053</t>
+  </si>
+  <si>
+    <t>0.9675,0.0037,0.0013,0.0162</t>
+  </si>
+  <si>
+    <t>0.1411,0.0159,0.0506,0.8589</t>
+  </si>
+  <si>
+    <t>0.9487,0.0106,0.0125,0.0124</t>
+  </si>
+  <si>
+    <t>0.0012,0.0268,0.9860,0.0075</t>
+  </si>
+  <si>
+    <t>0.1479,0.0057,0.0152,0.8946</t>
+  </si>
+  <si>
+    <t>0.8735,0.0015,0.0018,0.1345</t>
+  </si>
+  <si>
+    <t>0.8394,0.1234,0.0571,0.0089</t>
+  </si>
+  <si>
+    <t>0.9274,0.0217,0.0135,0.0141</t>
+  </si>
+  <si>
+    <t>0.9167,0.0477,0.0318,0.0049</t>
+  </si>
+  <si>
+    <t>0.4950,0.4269,0.1272,0.0924</t>
+  </si>
+  <si>
+    <t>0.8844,0.0566,0.0468,0.0091</t>
+  </si>
+  <si>
+    <t>0.8573,0.0494,0.0671,0.0231</t>
+  </si>
+  <si>
+    <t>0.9912,0.0038,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9829,0.0045,0.0007,0.0053</t>
+  </si>
+  <si>
+    <t>0.9885,0.0026,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.9831,0.0017,0.0015,0.0069</t>
+  </si>
+  <si>
+    <t>0.9857,0.0087,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9764,0.0250,0.0031,0.0010</t>
+  </si>
+  <si>
+    <t>0.9841,0.0081,0.0011,0.0028</t>
+  </si>
+  <si>
+    <t>0.9892,0.0021,0.0006,0.0031</t>
+  </si>
+  <si>
+    <t>0.6602,0.4068,0.0260,0.0043</t>
+  </si>
+  <si>
+    <t>0.7537,0.3223,0.0123,0.0008</t>
+  </si>
+  <si>
+    <t>0.7928,0.3680,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.8039,0.1223,0.1286,0.0086</t>
+  </si>
+  <si>
+    <t>0.9692,0.0207,0.0048,0.0030</t>
+  </si>
+  <si>
+    <t>0.8622,0.1164,0.0289,0.0131</t>
+  </si>
+  <si>
+    <t>0.9402,0.0740,0.0080,0.0022</t>
+  </si>
+  <si>
+    <t>0.9719,0.0171,0.0011,0.0043</t>
+  </si>
+  <si>
+    <t>0.0023,0.1031,0.9888,0.0007</t>
+  </si>
+  <si>
+    <t>0.9810,0.0085,0.0029,0.0016</t>
+  </si>
+  <si>
+    <t>0.0013,0.0045,0.9956,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0114,0.9840,0.0112</t>
+  </si>
+  <si>
+    <t>0.0144,0.0015,0.9873,0.0015</t>
+  </si>
+  <si>
+    <t>0.0097,0.0291,0.9747,0.0038</t>
+  </si>
+  <si>
+    <t>0.0188,0.0363,0.9673,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.0014,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0275,0.0080,0.9751,0.0019</t>
+  </si>
+  <si>
+    <t>0.1915,0.0181,0.8306,0.0196</t>
+  </si>
+  <si>
+    <t>0.0419,0.0163,0.9549,0.0030</t>
+  </si>
+  <si>
+    <t>0.5781,0.0177,0.4817,0.0107</t>
+  </si>
+  <si>
+    <t>0.5286,0.0437,0.5096,0.0051</t>
+  </si>
+  <si>
+    <t>0.2122,0.1666,0.6929,0.0115</t>
+  </si>
+  <si>
+    <t>0.6313,0.0199,0.3970,0.0049</t>
+  </si>
+  <si>
+    <t>0.2783,0.0417,0.7501,0.0118</t>
+  </si>
+  <si>
+    <t>0.4772,0.0393,0.5414,0.0352</t>
+  </si>
+  <si>
+    <t>0.8859,0.1797,0.0065,0.0013</t>
+  </si>
+  <si>
+    <t>0.7349,0.3992,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.9272,0.1121,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9097,0.1233,0.0044,0.0043</t>
+  </si>
+  <si>
+    <t>0.8921,0.1633,0.0055,0.0023</t>
+  </si>
+  <si>
+    <t>0.4803,0.3553,0.2680,0.1181</t>
+  </si>
+  <si>
+    <t>0.8245,0.0059,0.1222,0.0167</t>
+  </si>
+  <si>
+    <t>0.6096,0.0393,0.0945,0.2535</t>
+  </si>
+  <si>
+    <t>0.4487,0.0262,0.6267,0.0092</t>
+  </si>
+  <si>
+    <t>0.6975,0.0192,0.2122,0.0440</t>
+  </si>
+  <si>
+    <t>0.0065,0.0085,0.9855,0.0043</t>
+  </si>
+  <si>
+    <t>0.0227,0.4145,0.8114,0.0045</t>
+  </si>
+  <si>
+    <t>0.0017,0.2537,0.9809,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.2356,0.9805,0.0003</t>
+  </si>
+  <si>
+    <t>0.0056,0.6183,0.8382,0.0027</t>
+  </si>
+  <si>
+    <t>0.9926,0.0015,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9910,0.0050,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9918,0.0049,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9851,0.0101,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.9906,0.0070,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9794,0.0115,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.9915,0.0019,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9904,0.0022,0.0011,0.0021</t>
+  </si>
+  <si>
+    <t>0.3779,0.0344,0.7109,0.0076</t>
+  </si>
+  <si>
+    <t>0.6315,0.0974,0.3278,0.0072</t>
+  </si>
+  <si>
+    <t>0.8858,0.0179,0.0204,0.0538</t>
+  </si>
+  <si>
+    <t>0.0011,0.0039,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0225,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0158,0.0114,0.9769,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.0034,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.1030,0.0258,0.8860,0.0056</t>
+  </si>
+  <si>
+    <t>0.0002,0.0099,0.9981,0.0005</t>
+  </si>
+  <si>
+    <t>0.0127,0.1194,0.9485,0.0032</t>
+  </si>
+  <si>
+    <t>0.0712,0.0648,0.9130,0.0049</t>
+  </si>
+  <si>
+    <t>0.4608,0.0245,0.5068,0.0558</t>
+  </si>
+  <si>
+    <t>0.7275,0.0043,0.2662,0.0095</t>
+  </si>
+  <si>
+    <t>0.6918,0.0248,0.2933,0.0235</t>
+  </si>
+  <si>
+    <t>0.9783,0.0136,0.0025,0.0026</t>
+  </si>
+  <si>
+    <t>0.9908,0.0051,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9878,0.0084,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9823,0.0125,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9888,0.0031,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9873,0.0055,0.0009,0.0021</t>
+  </si>
+  <si>
+    <t>0.9840,0.0100,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.9867,0.0048,0.0012,0.0031</t>
+  </si>
+  <si>
+    <t>0.0530,0.2239,0.8279,0.0074</t>
+  </si>
+  <si>
+    <t>0.0008,0.0142,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0260,0.9896,0.0036</t>
+  </si>
+  <si>
+    <t>0.1098,0.0183,0.8977,0.0070</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9968,0.0032</t>
+  </si>
+  <si>
+    <t>0.1293,0.0396,0.3329,0.6079</t>
+  </si>
+  <si>
+    <t>0.1731,0.0161,0.8286,0.0290</t>
+  </si>
+  <si>
+    <t>0.0027,0.0358,0.9713,0.0152</t>
+  </si>
+  <si>
+    <t>0.8890,0.0034,0.0054,0.0810</t>
+  </si>
+  <si>
+    <t>0.0108,0.0230,0.0043,0.9881</t>
+  </si>
+  <si>
+    <t>0.0043,0.0096,0.0006,0.9963</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0009,0.0012,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.3974,0.0216,0.5169,0.1150</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2225,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2407,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3499,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3611,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3863,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4899,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5333,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5445,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
